--- a/library/03_Honkai_Star_Rail.xlsx
+++ b/library/03_Honkai_Star_Rail.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wuthering Waves" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wuthering Waves'!$A$1:$D$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -415,14 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -446,8 +437,534 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arcane</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ardelia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ember</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gilberta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Laevatain</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Last Rite</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lifeng</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Liino</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mi Fu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4.11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pogranichnik</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rossi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tangtang</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Typhoeus</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Yvonne</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Zhuang Fangyi</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6★</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alesh</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arclight</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Avywenna</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chen Qianyu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Da Pan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Perlica</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Purrchena</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Snowshine</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Wulfgard</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Xaihi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5★</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Akekuri</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4★</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Antal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4★</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Catcher</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4★</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Estella</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4★</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fluorite</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4★</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>